--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
   <si>
     <t/>
   </si>
@@ -92,15 +92,6 @@
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>20137755</t>
-  </si>
-  <si>
-    <t>HS  KRETEK FLTR20</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>20134734</t>
@@ -601,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1031,26 +1022,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -100,106 +100,106 @@
     <t>KPL SAKTI KRETEK 12S</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20137759</t>
+  </si>
+  <si>
+    <t>KPL/S  BLACK 12'S</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>20137759</t>
-  </si>
-  <si>
-    <t>KPL/S  BLACK 12'S</t>
+    <t>20134742</t>
+  </si>
+  <si>
+    <t>LAKON KRETEK 12'S</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20134742</t>
-  </si>
-  <si>
-    <t>LAKON KRETEK 12'S</t>
+    <t>20137757</t>
+  </si>
+  <si>
+    <t>OCHA  GUAVA 12'S</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>20137757</t>
-  </si>
-  <si>
-    <t>OCHA  GUAVA 12'S</t>
+    <t>20134733</t>
+  </si>
+  <si>
+    <t>POETRI KRETEK 12'S</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>20134733</t>
-  </si>
-  <si>
-    <t>POETRI KRETEK 12'S</t>
+    <t>20134739</t>
+  </si>
+  <si>
+    <t>POETRI MANGGA 12'S</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>20134739</t>
-  </si>
-  <si>
-    <t>POETRI MANGGA 12'S</t>
+    <t>20134740</t>
+  </si>
+  <si>
+    <t>VICTORY TEH MNS 12'S</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20134740</t>
-  </si>
-  <si>
-    <t>VICTORY TEH MNS 12'S</t>
+    <t>20140983</t>
+  </si>
+  <si>
+    <t>HS MILD ORGNL 16'S</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20140983</t>
-  </si>
-  <si>
-    <t>HS MILD ORGNL 16'S</t>
+    <t>20140982</t>
+  </si>
+  <si>
+    <t>HS MILD MANGO ICE 16</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20140982</t>
-  </si>
-  <si>
-    <t>HS MILD MANGO ICE 16</t>
+    <t>20140987</t>
+  </si>
+  <si>
+    <t>DJAVA FINE CUT 16'S</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20140987</t>
-  </si>
-  <si>
-    <t>DJAVA FINE CUT 16'S</t>
+    <t>20140988</t>
+  </si>
+  <si>
+    <t>KING DJAVA FLTR 20'S</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20140988</t>
-  </si>
-  <si>
-    <t>KING DJAVA FLTR 20'S</t>
+    <t>20140984</t>
+  </si>
+  <si>
+    <t>SEN FILTER 12'S</t>
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>20140984</t>
-  </si>
-  <si>
-    <t>SEN FILTER 12'S</t>
-  </si>
-  <si>
-    <t>21</t>
   </si>
 </sst>
 </file>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -200,6 +200,24 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>20130373</t>
+  </si>
+  <si>
+    <t>MAKNA ROKOK KRT 16'S</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20142560</t>
+  </si>
+  <si>
+    <t>HS  KRTK FILTER 12'S</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
 </sst>
 </file>
@@ -592,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1022,6 +1040,43 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>63</v>
       </c>
@@ -1055,6 +1055,9 @@
       </c>
       <c r="E22" s="1" t="s">
         <v>65</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
   <si>
     <t/>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>27</t>
+  </si>
+  <si>
+    <t>20143094</t>
+  </si>
+  <si>
+    <t>HS MILD PRPLE ICE 16</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
 </sst>
 </file>
@@ -610,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1080,6 +1089,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -139,24 +139,6 @@
     <t>13</t>
   </si>
   <si>
-    <t>20134739</t>
-  </si>
-  <si>
-    <t>POETRI MANGGA 12'S</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20134740</t>
-  </si>
-  <si>
-    <t>VICTORY TEH MNS 12'S</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20140983</t>
   </si>
   <si>
@@ -200,6 +182,15 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>20142548</t>
+  </si>
+  <si>
+    <t>KPL SAKTI  BLACK 16S</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>20130373</t>
@@ -619,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1089,26 +1080,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -145,79 +145,79 @@
     <t>HS MILD ORGNL 16'S</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20140982</t>
+  </si>
+  <si>
+    <t>HS MILD MANGO ICE 16</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20140987</t>
+  </si>
+  <si>
+    <t>DJAVA FINE CUT 16'S</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>20140982</t>
-  </si>
-  <si>
-    <t>HS MILD MANGO ICE 16</t>
+    <t>20140988</t>
+  </si>
+  <si>
+    <t>KING DJAVA FLTR 20'S</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20140987</t>
-  </si>
-  <si>
-    <t>DJAVA FINE CUT 16'S</t>
+    <t>20140984</t>
+  </si>
+  <si>
+    <t>SEN FILTER 12'S</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20140988</t>
-  </si>
-  <si>
-    <t>KING DJAVA FLTR 20'S</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20140984</t>
-  </si>
-  <si>
-    <t>SEN FILTER 12'S</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>20142548</t>
   </si>
   <si>
     <t>KPL SAKTI  BLACK 16S</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20130373</t>
+  </si>
+  <si>
+    <t>MAKNA ROKOK KRT 16'S</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20142560</t>
+  </si>
+  <si>
+    <t>HS  KRTK FILTER 12'S</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
-    <t>20130373</t>
-  </si>
-  <si>
-    <t>MAKNA ROKOK KRT 16'S</t>
+    <t>20143094</t>
+  </si>
+  <si>
+    <t>HS MILD PRPLE ICE 16</t>
   </si>
   <si>
     <t>26</t>
-  </si>
-  <si>
-    <t>20142560</t>
-  </si>
-  <si>
-    <t>HS  KRTK FILTER 12'S</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20143094</t>
-  </si>
-  <si>
-    <t>HS MILD PRPLE ICE 16</t>
-  </si>
-  <si>
-    <t>28</t>
   </si>
 </sst>
 </file>
